--- a/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69126</t>
+          <t>69012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76389</t>
+          <t>76489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76417</t>
+          <t>76884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84982</t>
+          <t>85023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148807</t>
+          <t>148512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159955</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169782</t>
+          <t>169701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180813</t>
+          <t>180533</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164691</t>
+          <t>165708</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177824</t>
+          <t>177975</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>339373</t>
+          <t>339989</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>355923</t>
+          <t>356523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>24329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76808</t>
+          <t>76497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83588</t>
+          <t>83546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84874</t>
+          <t>84965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96057</t>
+          <t>96271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164679</t>
+          <t>164949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177182</t>
+          <t>177590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132278</t>
+          <t>131997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143347</t>
+          <t>143077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136442</t>
+          <t>136144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144457</t>
+          <t>144293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271534</t>
+          <t>272974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>285558</t>
+          <t>286067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53681</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89101</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458560</t>
+          <t>459431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476834</t>
+          <t>477324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474868</t>
+          <t>475175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>494930</t>
+          <t>495850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>941691</t>
+          <t>941872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968995</t>
+          <t>969251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>22966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19474</t>
+          <t>19478</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22129</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>38624</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80345</t>
+          <t>81155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92820</t>
+          <t>93434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92569</t>
+          <t>92565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103581</t>
+          <t>103626</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177472</t>
+          <t>177539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194034</t>
+          <t>194565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20734</t>
+          <t>21038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12929</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>26553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24335</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43554</t>
+          <t>43487</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138610</t>
+          <t>138306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149876</t>
+          <t>150347</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>166294</t>
+          <t>166671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>180353</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309014</t>
+          <t>309081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>328233</t>
+          <t>327729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26405</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83197</t>
+          <t>82915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92934</t>
+          <t>93055</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86606</t>
+          <t>86365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96002</t>
+          <t>95800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>173388</t>
+          <t>173085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186611</t>
+          <t>186898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23323</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100962</t>
+          <t>100878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110626</t>
+          <t>110810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>118720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128021</t>
+          <t>127988</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>223898</t>
+          <t>224345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>237286</t>
+          <t>237229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>39011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61454</t>
+          <t>60340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39493</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>61357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83350</t>
+          <t>83051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114106</t>
+          <t>113810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>415511</t>
+          <t>416625</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438576</t>
+          <t>437954</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>476075</t>
+          <t>477424</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>499288</t>
+          <t>500543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>901640</t>
+          <t>901936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>932396</t>
+          <t>932695</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>22104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89347</t>
+          <t>89314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98110</t>
+          <t>98145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85744</t>
+          <t>85893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94204</t>
+          <t>94182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178390</t>
+          <t>178221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>190314</t>
+          <t>190378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26512</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27011</t>
+          <t>26661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45425</t>
+          <t>45502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131345</t>
+          <t>131945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143792</t>
+          <t>144338</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184080</t>
+          <t>184868</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>197754</t>
+          <t>198384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>320727</t>
+          <t>320650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>339141</t>
+          <t>339491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25299</t>
+          <t>25258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124645</t>
+          <t>124396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136278</t>
+          <t>136287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122256</t>
+          <t>122775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130072</t>
+          <t>130097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251186</t>
+          <t>251227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265308</t>
+          <t>264940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22071</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110491</t>
+          <t>109495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118856</t>
+          <t>118722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116214</t>
+          <t>116190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126060</t>
+          <t>125769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230039</t>
+          <t>231021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242831</t>
+          <t>243413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56558</t>
+          <t>55716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>28628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49272</t>
+          <t>48785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70008</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99045</t>
+          <t>96114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468127</t>
+          <t>468969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>489722</t>
+          <t>489964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>521115</t>
+          <t>521602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>541483</t>
+          <t>541759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996027</t>
+          <t>998958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1025064</t>
+          <t>1027149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48304</t>
+          <t>48646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55027</t>
+          <t>54876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53089</t>
+          <t>52496</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59700</t>
+          <t>59773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104572</t>
+          <t>104241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113821</t>
+          <t>113665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33284</t>
+          <t>34399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25288</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142388</t>
+          <t>142733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>152789</t>
+          <t>152973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>148394</t>
+          <t>147279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164553</t>
+          <t>164865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295596</t>
+          <t>295408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315268</t>
+          <t>315202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31499</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153632</t>
+          <t>153025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165296</t>
+          <t>165456</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195642</t>
+          <t>195760</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207210</t>
+          <t>207559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>353345</t>
+          <t>354485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369542</t>
+          <t>370623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>16185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35197</t>
+          <t>35094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>27278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>52571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251641</t>
+          <t>251495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264949</t>
+          <t>264442</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>269478</t>
+          <t>269581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288445</t>
+          <t>288490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525740</t>
+          <t>523651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>548913</t>
+          <t>548944</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51536</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49592</t>
+          <t>49117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77792</t>
+          <t>77960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85519</t>
+          <t>86545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>123106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>608753</t>
+          <t>609997</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>630301</t>
+          <t>630784</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>682496</t>
+          <t>682328</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710696</t>
+          <t>711171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1300330</t>
+          <t>1297471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1335058</t>
+          <t>1334032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6870</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11561</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4895</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9547</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9453</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6870</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3441</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11580</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81594</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76903</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>85068</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>73664</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>69012</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>76489</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69106</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76354</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>81594</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>76884</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>85023</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148512</t>
+          <t>148553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>159746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16209</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11035</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23812</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11155</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17545</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6842</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17603</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16209</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10756</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23023</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>20012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35988</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>172522</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>164919</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>177696</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>176091</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>169701</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>180533</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>169643</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>180404</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>172522</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>165708</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>177975</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>339989</t>
+          <t>340165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>356523</t>
+          <t>355965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12120</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7489</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18210</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5227</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2471</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9520</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2087</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9501</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12120</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6990</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18296</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24329</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>91141</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95772</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80790</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76497</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83546</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>76516</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>83930</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>91141</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>84965</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>96271</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164949</t>
+          <t>164656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177590</t>
+          <t>177459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86017</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86017</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86017</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6952</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3719</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11843</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11684</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7344</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18424</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7191</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17545</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6952</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3801</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11950</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>26602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>141142</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>136251</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>144375</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>138737</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>131997</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143077</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>132876</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>143230</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>141142</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>136144</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>144293</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>272974</t>
+          <t>271913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>286067</t>
+          <t>285514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>150421</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>150421</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>150421</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33274</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52542</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>32961</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24919</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42812</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24916</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42840</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,56%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>32699</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53374</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61541</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88920</t>
+          <t>88815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2208,74 +2208,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>486398</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>476007</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>495275</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>696</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>469282</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>459431</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>477324</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>459403</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>477327</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,44%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>95,04%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>486398</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>475175</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>495850</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1425</t>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>941872</t>
+          <t>941977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>969251</t>
+          <t>969244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>744</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>502243</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>502243</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>502243</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13292</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8399</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19764</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>16395</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10687</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22966</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10716</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23174</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>15,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13292</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8417</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19478</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>21902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>98751</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>92279</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>103644</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87726</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>81155</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>93434</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>80947</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>93405</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>84,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>77,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>98751</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>92565</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>103626</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,14%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177539</t>
+          <t>177752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194565</t>
+          <t>194261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18891</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12604</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27280</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14423</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8997</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21038</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9754</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21429</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18891</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12871</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26553</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24839</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43487</t>
+          <t>43765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>174333</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>165944</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>180620</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>144921</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>138306</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>150347</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>137915</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>149590</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,95%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>174333</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>166671</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>180353</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,22%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309081</t>
+          <t>308803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327729</t>
+          <t>327907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9936</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5766</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16179</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9026</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15065</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4932</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14880</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,21%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>5,03%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9936</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6012</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15447</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26708</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>91876</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>85633</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>96046</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>88954</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82915</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>93055</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>83100</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>93048</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,79%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>94,97%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>91876</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>86365</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95800</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,24%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>84,83%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>94,1%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>260</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>173085</t>
+          <t>172913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186898</t>
+          <t>187401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7268</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3743</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12628</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8645</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4710</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14642</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4732</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14255</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7268</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3714</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12982</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>124434</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>119074</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>127959</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>106875</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>100878</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>110810</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>101265</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>110788</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>124434</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>118720</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>127988</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224345</t>
+          <t>224469</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>237229</t>
+          <t>236819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4047,67 +4047,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38616</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>62296</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>48489</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>39011</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>60340</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>59783</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>49386</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38238</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>61357</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83051</t>
+          <t>84091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113810</t>
+          <t>114490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>489395</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>476485</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>500165</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>428476</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>416625</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>437954</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>417182</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>439163</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>489395</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>477424</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>500543</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>901936</t>
+          <t>901256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>932695</t>
+          <t>931655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6849</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3510</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12752</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8360</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4559</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13390</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4550</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13754</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6849</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3439</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11728</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>90772</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>84869</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>94111</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>94344</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>89314</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>98145</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>88950</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>98154</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>90772</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>85893</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>94182</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178221</t>
+          <t>177882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>190378</t>
+          <t>189866</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97621</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97621</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97621</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97621</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97621</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97621</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4965,67 +4965,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>18194</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12006</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25805</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>16878</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11222</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23615</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11406</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23747</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,85%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18194</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12208</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>25724</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26661</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45502</t>
+          <t>45934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>192398</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>184787</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>198586</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>138682</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>131945</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>144338</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>131813</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>144154</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,15%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>192398</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>184868</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>198384</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>320650</t>
+          <t>320218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>339491</t>
+          <t>339348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155560</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155560</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155560</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4949</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2208</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9407</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12871</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8027</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19918</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7732</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19898</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,92%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9396</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25258</t>
+          <t>25731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>127222</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>122764</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>129963</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>131443</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>124396</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>136287</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>124416</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>136582</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>127222</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>122775</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>130097</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251227</t>
+          <t>250754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>264940</t>
+          <t>264881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>7753</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3818</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13461</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>6614</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3384</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12611</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11742</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7753</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4235</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13814</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21089</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>122251</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>116543</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>126186</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>115492</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>109495</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>118722</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>110364</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>118771</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>122251</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>116190</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>125769</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231021</t>
+          <t>230312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243413</t>
+          <t>243081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28893</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>48170</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>44723</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34721</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55716</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>34354</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>55005</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,52%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>37745</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>28628</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>48785</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67923</t>
+          <t>69808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96114</t>
+          <t>97438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>532642</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>522217</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>541494</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>479962</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>468969</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>489964</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>469680</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>490331</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>532642</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>521602</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>541759</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>998958</t>
+          <t>997634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1027149</t>
+          <t>1025264</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>570387</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>570387</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>570387</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>789</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>524685</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>524685</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>524685</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>570387</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>570387</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>570387</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7067</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4954</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2635</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8865</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47171</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43470</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49186</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52557</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48646</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54876</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,39%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57327</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52496</t>
+          <t>42831</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>109884</t>
+          <t>94347</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>89706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113665</t>
+          <t>97919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18837</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12750</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25891</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10056</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5905</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16145</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34399</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33966</t>
+          <t>28487</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45148</t>
+          <t>37751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>137941</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>130887</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>144028</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>148822</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>142733</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>152973</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,67%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>157768</t>
+          <t>135501</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147279</t>
+          <t>129994</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164865</t>
+          <t>139345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>306590</t>
+          <t>273442</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295408</t>
+          <t>264178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315202</t>
+          <t>280761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156778</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156778</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156778</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>158878</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>158878</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>158878</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181678</t>
+          <t>145151</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181678</t>
+          <t>145151</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181678</t>
+          <t>145151</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>340556</t>
+          <t>301929</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340556</t>
+          <t>301929</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>340556</t>
+          <t>301929</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8877</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15634</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11964</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6898</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19329</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14221</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30359</t>
+          <t>29376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>191249</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>184492</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>195388</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>160390</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>153025</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>165456</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>203083</t>
+          <t>161758</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195760</t>
+          <t>154965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207559</t>
+          <t>166628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>363473</t>
+          <t>353006</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>354485</t>
+          <t>344671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>370623</t>
+          <t>360068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>172354</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>172354</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>172354</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173921</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173921</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384844</t>
+          <t>374047</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384844</t>
+          <t>374047</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384844</t>
+          <t>374047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23833</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16725</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35575</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12463</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7105</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20052</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24652</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16185</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35094</t>
+          <t>19803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,27 +7668,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37116</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27278</t>
+          <t>27205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52571</t>
+          <t>49570</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>267905</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>256163</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>275013</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>320</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>259084</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>251495</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>264442</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>280023</t>
+          <t>238965</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>269581</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288490</t>
+          <t>244007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,22 +7781,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>539106</t>
+          <t>506870</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>523651</t>
+          <t>494042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>548944</t>
+          <t>516407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>291738</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>291738</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>291738</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>271547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>271547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>271547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304675</t>
+          <t>251874</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304675</t>
+          <t>251874</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304675</t>
+          <t>251874</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>576222</t>
+          <t>543612</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>576222</t>
+          <t>543612</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>576222</t>
+          <t>543612</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54913</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42903</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69325</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29505</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50292</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>30673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77960</t>
+          <t>51187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>101524</t>
+          <t>94550</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86545</t>
+          <t>79571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123106</t>
+          <t>113243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>644266</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>629854</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>656276</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>874</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>620851</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>609997</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>630784</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,03%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>698202</t>
+          <t>583399</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>682328</t>
+          <t>571849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>711171</t>
+          <t>592363</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,17 +8124,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1319053</t>
+          <t>1227665</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1297471</t>
+          <t>1208972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1334032</t>
+          <t>1242644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699179</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699179</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699179</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>936</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>660289</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>660289</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>660289</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760288</t>
+          <t>623036</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760288</t>
+          <t>623036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760288</t>
+          <t>623036</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1420577</t>
+          <t>1322215</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1420577</t>
+          <t>1322215</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1420577</t>
+          <t>1322215</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
